--- a/backtest_runs/20260410_193731/by_symbol/PASL/PASL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/PASL/PASL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-3755.840000000003</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>108920.12</v>
@@ -679,7 +679,7 @@
         <v>-7981.159999999996</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>100938.96</v>
@@ -771,7 +771,7 @@
         <v>-3286.359999999992</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>105633.76</v>
@@ -817,7 +817,7 @@
         <v>-2347.400000000012</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>103286.36</v>
@@ -909,7 +909,7 @@
         <v>-5164.279999999994</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>106103.24</v>
@@ -955,7 +955,7 @@
         <v>-469.47999999999</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>105633.76</v>
@@ -1047,7 +1047,7 @@
         <v>-3286.360000000013</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>104225.32</v>
@@ -1185,7 +1185,7 @@
         <v>-5164.279999999994</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>105164.28</v>
@@ -1277,7 +1277,7 @@
         <v>-8920.119999999997</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>98122.08</v>
@@ -1415,7 +1415,7 @@
         <v>-2816.880000000002</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>97183.12</v>
@@ -1507,7 +1507,7 @@
         <v>-2816.880000000002</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>104694.8</v>
@@ -1645,7 +1645,7 @@
         <v>-6572.720000000006</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>115023.36</v>
